--- a/public/Nutzerstudie/Assets/Results/Analysis_Output/Feedback/00_Feedback_Auswertung.xlsx
+++ b/public/Nutzerstudie/Assets/Results/Analysis_Output/Feedback/00_Feedback_Auswertung.xlsx
@@ -735,16 +735,16 @@
         <v>2</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2.307692307692307</v>
+        <v>2.285714285714286</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -763,13 +763,13 @@
         <v>4</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>1.615384615384615</v>
+        <v>1.714285714285714</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
@@ -782,7 +782,7 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>4</v>
@@ -791,10 +791,10 @@
         <v>5</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>2.076923076923077</v>
+        <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -816,7 +816,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -985,7 +985,7 @@
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
@@ -994,19 +994,19 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -1036,19 +1036,19 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="28" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
@@ -1057,19 +1057,19 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
@@ -1099,10 +1099,10 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="6" t="n">
         <v>1</v>
@@ -1111,7 +1111,7 @@
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
@@ -1123,16 +1123,16 @@
         <v>3</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" ht="28" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
         </is>
       </c>
       <c r="B18" s="4" t="inlineStr">
@@ -1141,234 +1141,225 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E18" s="6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Vollständig</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
           <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
         </is>
       </c>
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Vollständig</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="C20" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>B. Objektive Ränge aus Identifikationsaufgaben</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Je Person: Mittel aus vier normalisierten Fehlern pro Methode; Rang 1 = kleinster Fehler. Nur vollständige 12 Identifikationsantworten. Gleichstände: Mittelränge.</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="42" customHeight="1">
-      <c r="A24" s="3" t="inlineStr">
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>participantId</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Vergleich_Status</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>Fehler_Mittel_VSUP_Prozent</t>
         </is>
       </c>
-      <c r="D24" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t>Fehler_Mittel_ScaledGlyph_Prozent</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
+      <c r="E25" s="3" t="inlineStr">
         <is>
           <t>Fehler_Mittel_IsoGlyph_Prozent</t>
         </is>
       </c>
-      <c r="F24" s="3" t="inlineStr">
+      <c r="F25" s="3" t="inlineStr">
         <is>
           <t>Objektiv_Rang_VSUP</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>Objektiv_Rang_ScaledGlyph</t>
         </is>
       </c>
-      <c r="H24" s="3" t="inlineStr">
+      <c r="H25" s="3" t="inlineStr">
         <is>
           <t>Objektiv_Rang_IsoGlyph</t>
         </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>42.38485817616743</v>
-      </c>
-      <c r="D25" s="7" t="n">
-        <v>31.5293682679196</v>
-      </c>
-      <c r="E25" s="7" t="n">
-        <v>60.34033321758997</v>
-      </c>
-      <c r="F25" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G25" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>29f255aa-1285-4664-9c07-0f88b583bd3b</t>
+          <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Subjektive Rangfolge unvollständig/ungültig</t>
+          <t>Vergleichbar</t>
         </is>
       </c>
       <c r="C26" s="7" t="n">
-        <v>45.53571296536033</v>
+        <v>42.38485817616743</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>64.4976938651715</v>
+        <v>31.5293682679196</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>41.81999831857323</v>
+        <v>60.34033321758997</v>
       </c>
       <c r="F26" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G26" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H26" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
+          <t>29f255aa-1285-4664-9c07-0f88b583bd3b</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Vergleichbar</t>
+          <t>Subjektive Rangfolge unvollständig/ungültig</t>
         </is>
       </c>
       <c r="C27" s="7" t="n">
-        <v>10.29036672907918</v>
+        <v>45.53571296536033</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>11.98323531419184</v>
+        <v>64.4976938651715</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>11.83143238102499</v>
+        <v>41.81999831857323</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="7" t="n">
         <v>3</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>500e39fd-101a-4580-a6be-ae82ef7f18b1</t>
+          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Keine 12 gültigen Identifikationsantworten</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>10.29036672907918</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>11.98323531419184</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>11.83143238102499</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
+          <t>500e39fd-101a-4580-a6be-ae82ef7f18b1</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>46.34694960507159</v>
-      </c>
-      <c r="D29" s="7" t="n">
-        <v>42.91459715690205</v>
-      </c>
-      <c r="E29" s="7" t="n">
-        <v>34.00200886019272</v>
-      </c>
-      <c r="F29" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G29" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" s="7" t="n">
-        <v>1</v>
-      </c>
+          <t>Keine 12 gültigen Identifikationsantworten</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="n"/>
+      <c r="F29" s="4" t="n"/>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
     </row>
     <row r="30" ht="28" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
@@ -1377,28 +1368,28 @@
         </is>
       </c>
       <c r="C30" s="7" t="n">
-        <v>1.3295434823672</v>
+        <v>46.34694960507159</v>
       </c>
       <c r="D30" s="7" t="n">
-        <v>1.844350504602159</v>
+        <v>42.91459715690205</v>
       </c>
       <c r="E30" s="7" t="n">
-        <v>5.063151098395346</v>
+        <v>34.00200886019272</v>
       </c>
       <c r="F30" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G30" s="7" t="n">
         <v>2</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" ht="28" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -1407,28 +1398,28 @@
         </is>
       </c>
       <c r="C31" s="7" t="n">
-        <v>34.36466488040803</v>
+        <v>49.81327459925297</v>
       </c>
       <c r="D31" s="7" t="n">
-        <v>20.73214147874743</v>
+        <v>35.69445889411599</v>
       </c>
       <c r="E31" s="7" t="n">
-        <v>34.98280439546281</v>
+        <v>27.82158271393961</v>
       </c>
       <c r="F31" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" ht="28" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B32" s="4" t="inlineStr">
@@ -1437,19 +1428,19 @@
         </is>
       </c>
       <c r="C32" s="7" t="n">
-        <v>36.05242019431911</v>
+        <v>1.3295434823672</v>
       </c>
       <c r="D32" s="7" t="n">
-        <v>19.89825987189952</v>
+        <v>1.844350504602159</v>
       </c>
       <c r="E32" s="7" t="n">
-        <v>43.17217895670172</v>
+        <v>5.063151098395346</v>
       </c>
       <c r="F32" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G32" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H32" s="7" t="n">
         <v>3</v>
@@ -1458,7 +1449,7 @@
     <row r="33" ht="28" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
@@ -1467,28 +1458,28 @@
         </is>
       </c>
       <c r="C33" s="7" t="n">
-        <v>7.038609725383625</v>
+        <v>34.36466488040803</v>
       </c>
       <c r="D33" s="7" t="n">
-        <v>0.8643181058856393</v>
+        <v>20.73214147874743</v>
       </c>
       <c r="E33" s="7" t="n">
-        <v>5.386747404976763</v>
+        <v>34.98280439546281</v>
       </c>
       <c r="F33" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="7" t="n">
         <v>1</v>
       </c>
       <c r="H33" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B34" s="4" t="inlineStr">
@@ -1497,28 +1488,28 @@
         </is>
       </c>
       <c r="C34" s="7" t="n">
-        <v>16.49148270993312</v>
+        <v>36.05242019431911</v>
       </c>
       <c r="D34" s="7" t="n">
-        <v>34.89915019264507</v>
+        <v>19.89825987189952</v>
       </c>
       <c r="E34" s="7" t="n">
-        <v>10.82804670491452</v>
+        <v>43.17217895670172</v>
       </c>
       <c r="F34" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G34" s="7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H34" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" ht="28" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -1527,13 +1518,13 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>13.35894261388807</v>
+        <v>7.038609725383625</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.07125293051291598</v>
+        <v>0.8643181058856393</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>1.683526764180344</v>
+        <v>5.386747404976763</v>
       </c>
       <c r="F35" s="7" t="n">
         <v>3</v>
@@ -1548,7 +1539,7 @@
     <row r="36" ht="28" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -1557,28 +1548,28 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>26.18357840309897</v>
+        <v>16.49148270993312</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>22.50612186177423</v>
+        <v>34.89915019264507</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>24.72618732288619</v>
+        <v>10.82804670491452</v>
       </c>
       <c r="F36" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G36" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H36" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" ht="28" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -1587,13 +1578,13 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>49.11114998014564</v>
+        <v>13.35894261388807</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>1.833357839286265</v>
+        <v>0.07125293051291598</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>14.66099819822692</v>
+        <v>1.683526764180344</v>
       </c>
       <c r="F37" s="7" t="n">
         <v>3</v>
@@ -1608,179 +1599,163 @@
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>26.18357840309897</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>22.50612186177423</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>24.72618732288619</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" ht="28" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>49.11114998014564</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>1.833357839286265</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>14.66099819822692</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" ht="28" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
           <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B40" s="4" t="inlineStr">
         <is>
           <t>Vergleichbar</t>
         </is>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="C40" s="7" t="n">
         <v>12.1492439381732</v>
       </c>
-      <c r="D38" s="7" t="n">
+      <c r="D40" s="7" t="n">
         <v>21.74093664114618</v>
       </c>
-      <c r="E38" s="7" t="n">
+      <c r="E40" s="7" t="n">
         <v>29.50535602420561</v>
       </c>
-      <c r="F38" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H38" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="2" t="inlineStr">
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>C. Subjektiv-objektiver Abgleich</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="40" customHeight="1">
-      <c r="A42" s="5" t="inlineStr">
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Rangdifferenz = subjektiver Rang minus objektiver Rang. Exakte Rangübereinstimmung pro Methode; Erstplatz stimmt überein, wenn die subjektive Lieblingsmethode objektiv den geringsten Durchschnittsfehler erzielt (einschließlich Gleichstand).</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="42" customHeight="1">
-      <c r="A43" s="3" t="inlineStr">
+    <row r="45" ht="42" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>participantId</t>
         </is>
       </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="B45" s="3" t="inlineStr">
         <is>
           <t>Vergleich_Status</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C45" s="3" t="inlineStr">
         <is>
           <t>Rangdifferenz_Sub_minus_Obj_VSUP</t>
         </is>
       </c>
-      <c r="D43" s="3" t="inlineStr">
+      <c r="D45" s="3" t="inlineStr">
         <is>
           <t>Rangdifferenz_Sub_minus_Obj_ScaledGlyph</t>
         </is>
       </c>
-      <c r="E43" s="3" t="inlineStr">
+      <c r="E45" s="3" t="inlineStr">
         <is>
           <t>Rangdifferenz_Sub_minus_Obj_IsoGlyph</t>
         </is>
       </c>
-      <c r="F43" s="3" t="inlineStr">
+      <c r="F45" s="3" t="inlineStr">
         <is>
           <t>Rang_uebereinstimmend_VSUP</t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
+      <c r="G45" s="3" t="inlineStr">
         <is>
           <t>Rang_uebereinstimmend_ScaledGlyph</t>
         </is>
       </c>
-      <c r="H43" s="3" t="inlineStr">
+      <c r="H45" s="3" t="inlineStr">
         <is>
           <t>Rang_uebereinstimmend_IsoGlyph</t>
         </is>
       </c>
-      <c r="I43" s="3" t="inlineStr">
+      <c r="I45" s="3" t="inlineStr">
         <is>
           <t>Anzahl_exakt_uebereinstimmend</t>
         </is>
       </c>
-      <c r="J43" s="3" t="inlineStr">
+      <c r="J45" s="3" t="inlineStr">
         <is>
           <t>Subjektiver_Erstplatz_objektiv_am_besten</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="28" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D44" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="28" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>29f255aa-1285-4664-9c07-0f88b583bd3b</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="inlineStr">
-        <is>
-          <t>Subjektive Rangfolge unvollständig/ungültig</t>
-        </is>
-      </c>
-      <c r="C45" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
     </row>
     <row r="46" ht="28" customHeight="1">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
+          <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
         </is>
       </c>
       <c r="B46" s="4" t="inlineStr">
@@ -1792,10 +1767,10 @@
         <v>1</v>
       </c>
       <c r="D46" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7" t="n">
         <v>-2</v>
-      </c>
-      <c r="E46" s="7" t="n">
-        <v>1</v>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
@@ -1824,27 +1799,39 @@
     <row r="47" ht="28" customHeight="1">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>500e39fd-101a-4580-a6be-ae82ef7f18b1</t>
+          <t>29f255aa-1285-4664-9c07-0f88b583bd3b</t>
         </is>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Keine 12 gültigen Identifikationsantworten</t>
-        </is>
-      </c>
-      <c r="C47" s="4" t="n"/>
+          <t>Subjektive Rangfolge unvollständig/ungültig</t>
+        </is>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>-1</v>
+      </c>
       <c r="D47" s="4" t="n"/>
-      <c r="E47" s="4" t="n"/>
-      <c r="F47" s="4" t="n"/>
+      <c r="E47" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
       <c r="I47" s="4" t="n"/>
       <c r="J47" s="4" t="n"/>
     </row>
     <row r="48" ht="28" customHeight="1">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
+          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
         </is>
       </c>
       <c r="B48" s="4" t="inlineStr">
@@ -1853,13 +1840,13 @@
         </is>
       </c>
       <c r="C48" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="D48" s="7" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E48" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
@@ -1888,51 +1875,27 @@
     <row r="49" ht="28" customHeight="1">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>500e39fd-101a-4580-a6be-ae82ef7f18b1</t>
         </is>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D49" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E49" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="H49" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
+          <t>Keine 12 gültigen Identifikationsantworten</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="n"/>
+      <c r="D49" s="4" t="n"/>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
     </row>
     <row r="50" ht="28" customHeight="1">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
         </is>
       </c>
       <c r="B50" s="4" t="inlineStr">
@@ -1941,17 +1904,17 @@
         </is>
       </c>
       <c r="C50" s="7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="D50" s="7" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="E50" s="7" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
@@ -1965,7 +1928,7 @@
         </is>
       </c>
       <c r="I50" s="6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
@@ -1976,7 +1939,7 @@
     <row r="51" ht="28" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
@@ -1985,13 +1948,13 @@
         </is>
       </c>
       <c r="C51" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="D51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" s="7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
@@ -2000,12 +1963,12 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
           <t>Ja</t>
-        </is>
-      </c>
-      <c r="H51" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
         </is>
       </c>
       <c r="I51" s="6" t="n">
@@ -2020,7 +1983,7 @@
     <row r="52" ht="28" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -2029,13 +1992,13 @@
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
@@ -2064,7 +2027,7 @@
     <row r="53" ht="28" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B53" s="4" t="inlineStr">
@@ -2076,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="D53" s="7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E53" s="7" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
@@ -2088,27 +2051,27 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="I53" s="6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
     </row>
     <row r="54" ht="28" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B54" s="4" t="inlineStr">
@@ -2117,42 +2080,42 @@
         </is>
       </c>
       <c r="C54" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D54" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E54" s="7" t="n">
         <v>-1</v>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
       <c r="I54" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
     </row>
     <row r="55" ht="28" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B55" s="4" t="inlineStr">
@@ -2161,42 +2124,42 @@
         </is>
       </c>
       <c r="C55" s="7" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="D55" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E55" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
       <c r="I55" s="6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
+          <t>Nein</t>
         </is>
       </c>
     </row>
     <row r="56" ht="28" customHeight="1">
       <c r="A56" s="4" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B56" s="4" t="inlineStr">
@@ -2205,17 +2168,17 @@
         </is>
       </c>
       <c r="C56" s="7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="D56" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E56" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -2225,11 +2188,11 @@
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>Nein</t>
+          <t>Ja</t>
         </is>
       </c>
       <c r="I56" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
@@ -2240,42 +2203,174 @@
     <row r="57" ht="28" customHeight="1">
       <c r="A57" s="4" t="inlineStr">
         <is>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="28" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="28" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="28" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
           <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
         </is>
       </c>
-      <c r="B57" s="4" t="inlineStr">
+      <c r="B60" s="4" t="inlineStr">
         <is>
           <t>Vergleichbar</t>
         </is>
       </c>
-      <c r="C57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
+      <c r="C60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G60" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
+      <c r="H60" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
       </c>
-      <c r="I57" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
+      <c r="I60" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>Ja</t>
         </is>
@@ -2283,13 +2378,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A44:J44"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
-    <mergeCell ref="A22:J22"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A42:J42"/>
-    <mergeCell ref="A41:J41"/>
+    <mergeCell ref="A43:J43"/>
+    <mergeCell ref="A24:J24"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2319,7 +2414,7 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -2461,7 +2556,7 @@
         <v>2</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
@@ -2487,46 +2582,46 @@
         <v>0</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M7" s="7" t="n">
         <v>3</v>
       </c>
       <c r="N7" s="7" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>4.642857142857143</v>
+        <v>4.8</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>2.023216892329291</v>
+        <v>2.042407542932745</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -2556,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7" t="n">
         <v>1</v>
@@ -2582,28 +2677,28 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="F9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>0</v>
@@ -2621,10 +2716,10 @@
         <v>3</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>4.714285714285714</v>
+        <v>4.8</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>1.898524586197294</v>
+        <v>1.859339360402736</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
@@ -2657,7 +2752,7 @@
         <v>3</v>
       </c>
       <c r="I10" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
@@ -2683,25 +2778,25 @@
         <v>0</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>0</v>
@@ -2713,16 +2808,16 @@
         <v>4</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>4.857142857142857</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>1.747840111378914</v>
+        <v>1.772810520855837</v>
       </c>
     </row>
   </sheetData>
@@ -2759,7 +2854,7 @@
     <col width="18" customWidth="1" min="13" max="13"/>
     <col width="18" customWidth="1" min="14" max="14"/>
     <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
     <col width="21" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
@@ -2898,7 +2993,7 @@
         <v>6</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" s="7" t="n">
         <v>0</v>
@@ -2924,28 +3019,28 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>0</v>
+        <v>6.67</v>
       </c>
       <c r="I7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>0</v>
@@ -2954,19 +3049,19 @@
         <v>4</v>
       </c>
       <c r="M7" s="7" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="N7" s="7" t="n">
         <v>5</v>
       </c>
       <c r="O7" s="7" t="n">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="P7" s="7" t="n">
-        <v>3.5</v>
+        <v>3.666666666666667</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>1.652503927610834</v>
+        <v>1.718249385968449</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -2999,7 +3094,7 @@
         <v>0</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
@@ -3025,25 +3120,25 @@
         <v>0</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="H9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>0</v>
@@ -3055,16 +3150,16 @@
         <v>2</v>
       </c>
       <c r="N9" s="7" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>3.357142857142857</v>
+        <v>3.6</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>1.499083969380217</v>
+        <v>1.723783214742669</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
@@ -3094,7 +3189,7 @@
         <v>4</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="7" t="n">
         <v>0</v>
@@ -3120,49 +3215,49 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="I11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="M11" s="7" t="n">
         <v>3</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>4.071428571428571</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>1.639150141632299</v>
+        <v>1.65615734242165</v>
       </c>
     </row>
   </sheetData>
@@ -3257,7 +3352,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
@@ -3275,13 +3370,13 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>3.230769230769226</v>
+        <v>2.285714285714278</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.1988141887380747</v>
+        <v>0.3189065573239717</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -3301,7 +3396,7 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
@@ -3319,13 +3414,13 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.4905660377358276</v>
+        <v>0.4642857142857184</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.7824830494337782</v>
+        <v>0.7928328533799686</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -3345,7 +3440,7 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
@@ -3363,13 +3458,13 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.7307692307692176</v>
+        <v>0.4727272727272769</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.6939297035054313</v>
+        <v>0.7894935331710372</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>

--- a/public/Nutzerstudie/Assets/Results/Analysis_Output/Feedback/00_Feedback_Auswertung.xlsx
+++ b/public/Nutzerstudie/Assets/Results/Analysis_Output/Feedback/00_Feedback_Auswertung.xlsx
@@ -10,10 +10,11 @@
     <sheet name="00_Lesehilfe" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Rangfolge" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Rang-Einzelantworten" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Ablesbarkeit" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Anstrengung" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Statistische Tests" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Freitext" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Praeferenz_je_Aufgabe" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Ablesbarkeit" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Anstrengung" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Statistische Tests" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Freitext" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -475,7 +476,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -496,7 +497,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="42" customHeight="1">
+    <row r="4" ht="36" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Begriff</t>
@@ -520,7 +521,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Subjektiver Rang</t>
@@ -532,7 +533,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Mittlerer subjektiver Rang</t>
@@ -544,7 +545,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Objektiver Rang</t>
@@ -556,7 +557,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Vollständigkeit</t>
@@ -568,7 +569,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Rangdifferenz</t>
@@ -580,7 +581,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Exakte Übereinstimmung</t>
@@ -592,49 +593,61 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="55" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
+          <t>Erstplatz je Einzelaufgabe</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Vergleich der subjektiv bevorzugten Methode mit der Methode mit dem geringsten normalisierten absoluten Fehler je Identifikationsaufgabe; nur vollständige Fälle. Objektive Gleichstände zählen als Übereinstimmung.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
           <t>Erstplatz-Übereinstimmung</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Ja, wenn die subjektiv auf Platz 1 gesetzte Methode den kleinsten persönlichen Durchschnittsfehler hat; objektive Gleichstände auf Platz 1 zählen ebenfalls.</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>Ablesbarkeit und Anstrengung</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Je Methode 7-stufige Antworten: Anzahl, Anteil gültiger Antworten und deskriptive Kennzahlen. Keine Änderung der bisherigen Berechnungen.</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>Friedman und Wilcoxon</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Friedman prüft Unterschiede zwischen den drei verbundenen Feedbackbewertungen; bei p &lt; 0,05 folgen paarweise Wilcoxon-Tests mit Holm-Korrektur innerhalb des Merkmals.</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>Interpretation</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Die Übereinstimmung beschreibt, ob persönliche Präferenz und Identifikationsgenauigkeit zusammenfallen; sie beweist keine Ursache und ist kein zusätzlicher Signifikanztest.</t>
         </is>
@@ -662,7 +675,7 @@
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
   </cols>
@@ -688,7 +701,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Methode</t>
@@ -732,19 +745,19 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>6</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2.285714285714286</v>
+        <v>2.1875</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>1</v>
@@ -760,16 +773,16 @@
         <v>7</v>
       </c>
       <c r="C7" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="6" t="n">
-        <v>3</v>
-      </c>
       <c r="E7" s="7" t="n">
-        <v>1.714285714285714</v>
+        <v>1.8125</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G7" s="6" t="n">
         <v>1</v>
@@ -782,19 +795,19 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>1</v>
@@ -816,7 +829,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -852,7 +865,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>participantId</t>
@@ -879,7 +892,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
@@ -900,7 +913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>29f255aa-1285-4664-9c07-0f88b583bd3b</t>
@@ -919,7 +932,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
@@ -940,7 +953,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>500e39fd-101a-4580-a6be-ae82ef7f18b1</t>
@@ -961,7 +974,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
@@ -982,7 +995,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
@@ -1003,7 +1016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
@@ -1024,7 +1037,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" ht="28" customHeight="1">
+    <row r="13" ht="40" customHeight="1">
       <c r="A13" s="4" t="inlineStr">
         <is>
           <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
@@ -1045,7 +1058,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" ht="28" customHeight="1">
+    <row r="14" ht="40" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
           <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
@@ -1066,7 +1079,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" ht="28" customHeight="1">
+    <row r="15" ht="40" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
@@ -1087,7 +1100,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="28" customHeight="1">
+    <row r="16" ht="40" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
@@ -1108,7 +1121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" ht="28" customHeight="1">
+    <row r="17" ht="40" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
@@ -1129,7 +1142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="28" customHeight="1">
+    <row r="18" ht="40" customHeight="1">
       <c r="A18" s="4" t="inlineStr">
         <is>
           <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
@@ -1150,7 +1163,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" ht="28" customHeight="1">
+    <row r="19" ht="40" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
@@ -1171,7 +1184,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
+    <row r="20" ht="40" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
@@ -1192,324 +1205,306 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Vollständig</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Vollständig</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>B. Objektive Ränge aus Identifikationsaufgaben</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="5" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Je Person: Mittel aus vier normalisierten Fehlern pro Methode; Rang 1 = kleinster Fehler. Nur vollständige 12 Identifikationsantworten. Gleichstände: Mittelränge.</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="42" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>participantId</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Vergleich_Status</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Fehler_Mittel_VSUP_Prozent</t>
         </is>
       </c>
-      <c r="D25" s="3" t="inlineStr">
+      <c r="D27" s="3" t="inlineStr">
         <is>
           <t>Fehler_Mittel_ScaledGlyph_Prozent</t>
         </is>
       </c>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>Fehler_Mittel_IsoGlyph_Prozent</t>
         </is>
       </c>
-      <c r="F25" s="3" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>Objektiv_Rang_VSUP</t>
         </is>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
         <is>
           <t>Objektiv_Rang_ScaledGlyph</t>
         </is>
       </c>
-      <c r="H25" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>Objektiv_Rang_IsoGlyph</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
         </is>
       </c>
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B28" s="4" t="inlineStr">
         <is>
           <t>Vergleichbar</t>
         </is>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="C28" s="7" t="n">
         <v>42.38485817616743</v>
       </c>
-      <c r="D26" s="7" t="n">
+      <c r="D28" s="7" t="n">
         <v>31.5293682679196</v>
       </c>
-      <c r="E26" s="7" t="n">
+      <c r="E28" s="7" t="n">
         <v>60.34033321758997</v>
       </c>
-      <c r="F26" s="7" t="n">
+      <c r="F28" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G26" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="7" t="n">
+      <c r="G28" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>29f255aa-1285-4664-9c07-0f88b583bd3b</t>
         </is>
       </c>
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Subjektive Rangfolge unvollständig/ungültig</t>
         </is>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="C29" s="7" t="n">
         <v>45.53571296536033</v>
       </c>
-      <c r="D27" s="7" t="n">
+      <c r="D29" s="7" t="n">
         <v>64.4976938651715</v>
       </c>
-      <c r="E27" s="7" t="n">
+      <c r="E29" s="7" t="n">
         <v>41.81999831857323</v>
       </c>
-      <c r="F27" s="7" t="n">
+      <c r="F29" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="G27" s="7" t="n">
+      <c r="G29" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H27" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="H29" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
         </is>
       </c>
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B30" s="4" t="inlineStr">
         <is>
           <t>Vergleichbar</t>
         </is>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="C30" s="7" t="n">
         <v>10.29036672907918</v>
       </c>
-      <c r="D28" s="7" t="n">
+      <c r="D30" s="7" t="n">
         <v>11.98323531419184</v>
       </c>
-      <c r="E28" s="7" t="n">
+      <c r="E30" s="7" t="n">
         <v>11.83143238102499</v>
       </c>
-      <c r="F28" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" s="7" t="n">
+      <c r="F30" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G30" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H28" s="7" t="n">
+      <c r="H30" s="7" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="29" ht="28" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>500e39fd-101a-4580-a6be-ae82ef7f18b1</t>
         </is>
       </c>
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t>Keine 12 gültigen Identifikationsantworten</t>
         </is>
       </c>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="4" t="n"/>
-      <c r="F29" s="4" t="n"/>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-    </row>
-    <row r="30" ht="28" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
         </is>
       </c>
-      <c r="B30" s="4" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t>Vergleichbar</t>
         </is>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="C32" s="7" t="n">
         <v>46.34694960507159</v>
       </c>
-      <c r="D30" s="7" t="n">
+      <c r="D32" s="7" t="n">
         <v>42.91459715690205</v>
       </c>
-      <c r="E30" s="7" t="n">
+      <c r="E32" s="7" t="n">
         <v>34.00200886019272</v>
       </c>
-      <c r="F30" s="7" t="n">
+      <c r="F32" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="G30" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>49.81327459925297</v>
-      </c>
-      <c r="D31" s="7" t="n">
-        <v>35.69445889411599</v>
-      </c>
-      <c r="E31" s="7" t="n">
-        <v>27.82158271393961</v>
-      </c>
-      <c r="F31" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G31" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H31" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" ht="28" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>1.3295434823672</v>
-      </c>
-      <c r="D32" s="7" t="n">
-        <v>1.844350504602159</v>
-      </c>
-      <c r="E32" s="7" t="n">
-        <v>5.063151098395346</v>
-      </c>
-      <c r="F32" s="7" t="n">
-        <v>1</v>
       </c>
       <c r="G32" s="7" t="n">
         <v>2</v>
       </c>
       <c r="H32" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C33" s="7" t="n">
+        <v>49.81327459925297</v>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>35.69445889411599</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>27.82158271393961</v>
+      </c>
+      <c r="F33" s="7" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" ht="28" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="G33" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>Vergleichbar</t>
         </is>
       </c>
-      <c r="C33" s="7" t="n">
-        <v>34.36466488040803</v>
-      </c>
-      <c r="D33" s="7" t="n">
-        <v>20.73214147874743</v>
-      </c>
-      <c r="E33" s="7" t="n">
-        <v>34.98280439546281</v>
-      </c>
-      <c r="F33" s="7" t="n">
+      <c r="C34" s="7" t="n">
+        <v>1.3295434823672</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>1.844350504602159</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>5.063151098395346</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
         <v>2</v>
-      </c>
-      <c r="G33" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" ht="28" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>36.05242019431911</v>
-      </c>
-      <c r="D34" s="7" t="n">
-        <v>19.89825987189952</v>
-      </c>
-      <c r="E34" s="7" t="n">
-        <v>43.17217895670172</v>
-      </c>
-      <c r="F34" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G34" s="7" t="n">
-        <v>1</v>
       </c>
       <c r="H34" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="35" ht="28" customHeight="1">
+    <row r="35" ht="40" customHeight="1">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
         </is>
       </c>
       <c r="B35" s="4" t="inlineStr">
@@ -1518,28 +1513,28 @@
         </is>
       </c>
       <c r="C35" s="7" t="n">
-        <v>7.038609725383625</v>
+        <v>34.36466488040803</v>
       </c>
       <c r="D35" s="7" t="n">
-        <v>0.8643181058856393</v>
+        <v>20.73214147874743</v>
       </c>
       <c r="E35" s="7" t="n">
-        <v>5.386747404976763</v>
+        <v>34.98280439546281</v>
       </c>
       <c r="F35" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H35" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G35" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" ht="28" customHeight="1">
+    </row>
+    <row r="36" ht="40" customHeight="1">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B36" s="4" t="inlineStr">
@@ -1548,28 +1543,28 @@
         </is>
       </c>
       <c r="C36" s="7" t="n">
-        <v>16.49148270993312</v>
+        <v>36.05242019431911</v>
       </c>
       <c r="D36" s="7" t="n">
-        <v>34.89915019264507</v>
+        <v>19.89825987189952</v>
       </c>
       <c r="E36" s="7" t="n">
-        <v>10.82804670491452</v>
+        <v>43.17217895670172</v>
       </c>
       <c r="F36" s="7" t="n">
         <v>2</v>
       </c>
       <c r="G36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="H36" s="7" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" ht="28" customHeight="1">
+    </row>
+    <row r="37" ht="40" customHeight="1">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
         </is>
       </c>
       <c r="B37" s="4" t="inlineStr">
@@ -1578,13 +1573,13 @@
         </is>
       </c>
       <c r="C37" s="7" t="n">
-        <v>13.35894261388807</v>
+        <v>7.038609725383625</v>
       </c>
       <c r="D37" s="7" t="n">
-        <v>0.07125293051291598</v>
+        <v>0.8643181058856393</v>
       </c>
       <c r="E37" s="7" t="n">
-        <v>1.683526764180344</v>
+        <v>5.386747404976763</v>
       </c>
       <c r="F37" s="7" t="n">
         <v>3</v>
@@ -1596,10 +1591,10 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" ht="28" customHeight="1">
+    <row r="38" ht="40" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B38" s="4" t="inlineStr">
@@ -1608,28 +1603,28 @@
         </is>
       </c>
       <c r="C38" s="7" t="n">
-        <v>26.18357840309897</v>
+        <v>16.49148270993312</v>
       </c>
       <c r="D38" s="7" t="n">
-        <v>22.50612186177423</v>
+        <v>34.89915019264507</v>
       </c>
       <c r="E38" s="7" t="n">
-        <v>24.72618732288619</v>
+        <v>10.82804670491452</v>
       </c>
       <c r="F38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="G38" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="H38" s="7" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="39" ht="28" customHeight="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B39" s="4" t="inlineStr">
@@ -1638,13 +1633,13 @@
         </is>
       </c>
       <c r="C39" s="7" t="n">
-        <v>49.11114998014564</v>
+        <v>13.35894261388807</v>
       </c>
       <c r="D39" s="7" t="n">
-        <v>1.833357839286265</v>
+        <v>0.07125293051291598</v>
       </c>
       <c r="E39" s="7" t="n">
-        <v>14.66099819822692</v>
+        <v>1.683526764180344</v>
       </c>
       <c r="F39" s="7" t="n">
         <v>3</v>
@@ -1656,261 +1651,241 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" ht="28" customHeight="1">
+    <row r="40" ht="40" customHeight="1">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>26.18357840309897</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>22.50612186177423</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>24.72618732288619</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="n">
+        <v>49.11114998014564</v>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>1.833357839286265</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>14.66099819822692</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G41" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
           <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
         </is>
       </c>
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B42" s="4" t="inlineStr">
         <is>
           <t>Vergleichbar</t>
         </is>
       </c>
-      <c r="C40" s="7" t="n">
+      <c r="C42" s="7" t="n">
         <v>12.1492439381732</v>
       </c>
-      <c r="D40" s="7" t="n">
+      <c r="D42" s="7" t="n">
         <v>21.74093664114618</v>
       </c>
-      <c r="E40" s="7" t="n">
+      <c r="E42" s="7" t="n">
         <v>29.50535602420561</v>
       </c>
-      <c r="F40" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" s="7" t="n">
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="H40" s="7" t="n">
+      <c r="H42" s="7" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="n">
+        <v>25.18735311364372</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>7.378459850048434</v>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>0.8438727597692077</v>
+      </c>
+      <c r="F43" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="G43" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>0.2925711539883867</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>1.625318021192256</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>0.9551514136555512</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>C. Subjektiv-objektiver Abgleich</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="40" customHeight="1">
-      <c r="A44" s="5" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>Rangdifferenz = subjektiver Rang minus objektiver Rang. Exakte Rangübereinstimmung pro Methode; Erstplatz stimmt überein, wenn die subjektive Lieblingsmethode objektiv den geringsten Durchschnittsfehler erzielt (einschließlich Gleichstand).</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="42" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="49" ht="45" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
         <is>
           <t>participantId</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B49" s="3" t="inlineStr">
         <is>
           <t>Vergleich_Status</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C49" s="3" t="inlineStr">
         <is>
           <t>Rangdifferenz_Sub_minus_Obj_VSUP</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D49" s="3" t="inlineStr">
         <is>
           <t>Rangdifferenz_Sub_minus_Obj_ScaledGlyph</t>
         </is>
       </c>
-      <c r="E45" s="3" t="inlineStr">
+      <c r="E49" s="3" t="inlineStr">
         <is>
           <t>Rangdifferenz_Sub_minus_Obj_IsoGlyph</t>
         </is>
       </c>
-      <c r="F45" s="3" t="inlineStr">
+      <c r="F49" s="3" t="inlineStr">
         <is>
           <t>Rang_uebereinstimmend_VSUP</t>
         </is>
       </c>
-      <c r="G45" s="3" t="inlineStr">
+      <c r="G49" s="3" t="inlineStr">
         <is>
           <t>Rang_uebereinstimmend_ScaledGlyph</t>
         </is>
       </c>
-      <c r="H45" s="3" t="inlineStr">
+      <c r="H49" s="3" t="inlineStr">
         <is>
           <t>Rang_uebereinstimmend_IsoGlyph</t>
         </is>
       </c>
-      <c r="I45" s="3" t="inlineStr">
+      <c r="I49" s="3" t="inlineStr">
         <is>
           <t>Anzahl_exakt_uebereinstimmend</t>
         </is>
       </c>
-      <c r="J45" s="3" t="inlineStr">
+      <c r="J49" s="3" t="inlineStr">
         <is>
           <t>Subjektiver_Erstplatz_objektiv_am_besten</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="28" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
         </is>
       </c>
-      <c r="B46" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Vergleichbar</t>
         </is>
       </c>
-      <c r="C46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="7" t="n">
+      <c r="C50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E50" s="7" t="n">
         <v>-2</v>
-      </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="H46" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="28" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>29f255aa-1285-4664-9c07-0f88b583bd3b</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Subjektive Rangfolge unvollständig/ungültig</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-    </row>
-    <row r="48" ht="28" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D48" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="E48" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="H48" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="28" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>500e39fd-101a-4580-a6be-ae82ef7f18b1</t>
-        </is>
-      </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Keine 12 gültigen Identifikationsantworten</t>
-        </is>
-      </c>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="4" t="n"/>
-      <c r="F49" s="4" t="n"/>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
-    </row>
-    <row r="50" ht="28" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
-        </is>
-      </c>
-      <c r="B50" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C50" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D50" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E50" s="7" t="n">
-        <v>2</v>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
@@ -1936,54 +1911,42 @@
         </is>
       </c>
     </row>
-    <row r="51" ht="28" customHeight="1">
+    <row r="51" ht="40" customHeight="1">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
+          <t>29f255aa-1285-4664-9c07-0f88b583bd3b</t>
         </is>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Vergleichbar</t>
+          <t>Subjektive Rangfolge unvollständig/ungültig</t>
         </is>
       </c>
       <c r="C51" s="7" t="n">
         <v>-1</v>
       </c>
-      <c r="D51" s="7" t="n">
-        <v>1</v>
-      </c>
+      <c r="D51" s="4" t="n"/>
       <c r="E51" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
           <t>Nein</t>
         </is>
       </c>
-      <c r="G51" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
+      <c r="G51" s="4" t="n"/>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J51" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="28" customHeight="1">
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+    </row>
+    <row r="52" ht="40" customHeight="1">
       <c r="A52" s="4" t="inlineStr">
         <is>
-          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
         </is>
       </c>
       <c r="B52" s="4" t="inlineStr">
@@ -1992,13 +1955,13 @@
         </is>
       </c>
       <c r="C52" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D52" s="7" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="E52" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
@@ -2024,186 +1987,162 @@
         </is>
       </c>
     </row>
-    <row r="53" ht="28" customHeight="1">
+    <row r="53" ht="40" customHeight="1">
       <c r="A53" s="4" t="inlineStr">
         <is>
+          <t>500e39fd-101a-4580-a6be-ae82ef7f18b1</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Keine 12 gültigen Identifikationsantworten</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C53" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E53" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="28" customHeight="1">
-      <c r="A54" s="4" t="inlineStr">
-        <is>
-          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C54" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="D54" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F54" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="H54" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="28" customHeight="1">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C55" s="7" t="n">
-        <v>-2</v>
-      </c>
-      <c r="D55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F55" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="H55" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="28" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="H56" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="28" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
         </is>
       </c>
       <c r="B57" s="4" t="inlineStr">
@@ -2215,10 +2154,10 @@
         <v>0</v>
       </c>
       <c r="D57" s="7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" s="7" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
@@ -2244,10 +2183,10 @@
         </is>
       </c>
     </row>
-    <row r="58" ht="28" customHeight="1">
+    <row r="58" ht="40" customHeight="1">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
@@ -2256,86 +2195,86 @@
         </is>
       </c>
       <c r="C58" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D58" s="7" t="n">
         <v>0</v>
       </c>
       <c r="E58" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C59" s="7" t="n">
+        <v>-2</v>
+      </c>
+      <c r="D59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="H58" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="28" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
-        </is>
-      </c>
-      <c r="B59" s="4" t="inlineStr">
-        <is>
-          <t>Vergleichbar</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D59" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F59" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>Ja</t>
-        </is>
-      </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Nein</t>
-        </is>
-      </c>
-      <c r="I59" s="6" t="n">
-        <v>1</v>
-      </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>Ja</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="28" customHeight="1">
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
       <c r="A60" s="4" t="inlineStr">
         <is>
-          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
         </is>
       </c>
       <c r="B60" s="4" t="inlineStr">
@@ -2376,15 +2315,279 @@
         </is>
       </c>
     </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Vergleichbar</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+      <c r="I66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A44:J44"/>
+    <mergeCell ref="A47:J47"/>
     <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A23:J23"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A43:J43"/>
-    <mergeCell ref="A24:J24"/>
+    <mergeCell ref="A48:J48"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="A25:J25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2396,435 +2599,2349 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q11"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="18" customWidth="1" min="14" max="14"/>
-    <col width="18" customWidth="1" min="15" max="15"/>
-    <col width="18" customWidth="1" min="16" max="16"/>
-    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="39" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="29" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Feedback: Ablesbarkeit</t>
+          <t>Subjektive Erstplatzierung und Genauigkeit je Einzelaufgabe</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Antwortverteilung und Kennzahlen</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="40" customHeight="1">
+          <t>A. Übereinstimmung nach Identifikationsaufgabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Stufe 1–7: Anzahl und prozentualer Anteil; Median, Quartile, IQR, Mittelwert und Standardabweichung basieren auf gültigen Antworten.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="42" customHeight="1">
+          <t>Anzahl und Anteil der Personen, deren subjektiv bevorzugte Methode je Aufgabe den kleinsten normalisierten Fehler erzielt.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>Methode</t>
+          <t>Aufgabe</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Angabe</t>
+          <t>n_vergleichbar</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Stufe 1</t>
+          <t>n_Uebereinstimmung</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Stufe 2</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>Stufe 3</t>
-        </is>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t>Stufe 4</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>Stufe 5</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>Stufe 6</t>
-        </is>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>Stufe 7</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>Fehlend</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t>Median</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t>Q3</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>IQR</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>Mittelwert</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>Standardabweichung</t>
+          <t>Anteil_Uebereinstimmung_%</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Anzahl</t>
-        </is>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>0</v>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="I6" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="4" t="n"/>
-      <c r="L6" s="4" t="n"/>
-      <c r="M6" s="4" t="n"/>
-      <c r="N6" s="4" t="n"/>
-      <c r="O6" s="4" t="n"/>
-      <c r="P6" s="4" t="n"/>
-      <c r="Q6" s="4" t="n"/>
+        <v>26.66666666666667</v>
+      </c>
     </row>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>VSUP</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Prozent (%)</t>
-        </is>
-      </c>
-      <c r="C7" s="7" t="n">
-        <v>0</v>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>7</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" s="7" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="F7" s="7" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="G7" s="7" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="H7" s="7" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="I7" s="7" t="n">
-        <v>33.33</v>
-      </c>
-      <c r="J7" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K7" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="O7" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="P7" s="7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q7" s="7" t="n">
-        <v>2.042407542932745</v>
+        <v>46.66666666666666</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>Scaled Glyph</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Anzahl</t>
-        </is>
-      </c>
-      <c r="C8" s="7" t="n">
-        <v>1</v>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="7" t="n">
-        <v>8</v>
-      </c>
-      <c r="I8" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-      <c r="M8" s="4" t="n"/>
-      <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="n"/>
-      <c r="P8" s="4" t="n"/>
-      <c r="Q8" s="4" t="n"/>
+        <v>60</v>
+      </c>
     </row>
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Scaled Glyph</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Prozent (%)</t>
-        </is>
-      </c>
-      <c r="C9" s="7" t="n">
-        <v>6.67</v>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>15</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>9</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="E9" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="7" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>B. Individueller Vergleich je Aufgabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Nur vollständige subjektive Rangfolgen und zwölf gültige Identifikationsantworten; bei gleichem minimalem Fehler gelten mehrere Methoden als objektiv genaueste.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Teilnehmer</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Aufgabe</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Subjektiv_bevorzugt</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Fehler_VSUP_Prozent</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Fehler_ScaledGlyph_Prozent</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Fehler_IsoGlyph_Prozent</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Objektiv_genaueste_Methode</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Erstplatz_ist_genaueste</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>31.30507552403889</v>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>30.88375849416899</v>
+      </c>
+      <c r="F15" s="7" t="n">
+        <v>99.80351839383717</v>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>1.033718543057625</v>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>1.365339659687163</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>0.533568162776351</v>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="40" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>99.82703565726457</v>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>68.81378549290919</v>
+      </c>
+      <c r="F17" s="7" t="n">
+        <v>41.02424631374638</v>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="40" customHeight="1">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>08e4cf92-36c9-4904-af75-845c4216238d</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>37.37360298030865</v>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>25.05458942491307</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="40" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>38.15309738109182</v>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>42.31382876620111</v>
+      </c>
+      <c r="F19" s="7" t="n">
+        <v>43.77674525882834</v>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>0.6983955190085469</v>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>2.316354452811438</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>0.6291348459936146</v>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="40" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>2.268689540744398</v>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0.8348855774347732</v>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="40" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0.04128447547194585</v>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>3.126663118680212</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>2.084963841843242</v>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="40" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>41.55797675598935</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>61.00786621463389</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>47.02889312996408</v>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="40" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>49.21226069632303</v>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>0.9541491856630114</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>1.040861623332128</v>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="40" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>50.5276977741601</v>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>55.87433083930759</v>
+      </c>
+      <c r="F25" s="7" t="n">
+        <v>71.21082866355709</v>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="40" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>5ec895f4-c4a9-4096-8048-bf78c36aeb0e</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>44.08986319381388</v>
+      </c>
+      <c r="E26" s="7" t="n">
+        <v>53.82204238800372</v>
+      </c>
+      <c r="F26" s="7" t="n">
+        <v>16.7274520239176</v>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="40" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>99.9960434933357</v>
+      </c>
+      <c r="E27" s="7" t="n">
+        <v>5.018128007253322</v>
+      </c>
+      <c r="F27" s="7" t="n">
+        <v>25.25940816197958</v>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="40" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>0.007414919955298784</v>
+      </c>
+      <c r="E28" s="7" t="n">
+        <v>3.556595776329476</v>
+      </c>
+      <c r="F28" s="7" t="n">
+        <v>0.2366086969719</v>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="40" customHeight="1">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>96.69489402999095</v>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>74.94541057508692</v>
+      </c>
+      <c r="F29" s="7" t="n">
+        <v>84.15380521554034</v>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="40" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>5fd06c65-e3be-48d2-b325-94c1e27a7f6d</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="n">
+        <v>2.554745953729939</v>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>59.25770121779424</v>
+      </c>
+      <c r="F30" s="7" t="n">
+        <v>1.636508781266623</v>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="40" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>5.018128007253322</v>
+      </c>
+      <c r="E31" s="7" t="n">
+        <v>4.612880656014729</v>
+      </c>
+      <c r="F31" s="7" t="n">
+        <v>17.09910497159589</v>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="40" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="n">
+        <v>0.02259859416251884</v>
+      </c>
+      <c r="E32" s="7" t="n">
+        <v>1.31095563594379</v>
+      </c>
+      <c r="F32" s="7" t="n">
+        <v>0.0411195578526509</v>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="40" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n">
+        <v>0.2361628525810126</v>
+      </c>
+      <c r="E33" s="7" t="n">
+        <v>0.2361628525810126</v>
+      </c>
+      <c r="F33" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="40" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>0.04128447547194585</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>1.217402873869105</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>2.936284945058243</v>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="40" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>41.02216929182877</v>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>41.55797675598935</v>
+      </c>
+      <c r="F35" s="7" t="n">
+        <v>39.56135878519856</v>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="40" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>2.181097812059075</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>38.99213378536611</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>0.5459537157273002</v>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="40" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="E37" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="F37" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>53.33</v>
-      </c>
-      <c r="I9" s="7" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="J9" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K9" s="7" t="n">
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="40" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>97d6c4cc-40ac-442f-b283-2f1d22c2cbcd</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>94.07929749866966</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>2.202360454559643</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>99.8239050809254</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="40" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>38.15309738109182</v>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>32.21321139546893</v>
+      </c>
+      <c r="F39" s="7" t="n">
+        <v>44.89455276555509</v>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="40" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>3.549774392647167</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>1.75226493275167</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>0.5595185381948814</v>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="40" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="n">
+        <v>43.11273205397098</v>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>42.39622139435863</v>
+      </c>
+      <c r="F41" s="7" t="n">
+        <v>43.82552515418088</v>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="40" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>59.39407694956648</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>3.231341765018832</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>83.40911936887602</v>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="40" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>27.98108584543508</v>
+      </c>
+      <c r="E43" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>6</v>
-      </c>
-      <c r="O9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="P9" s="7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="Q9" s="7" t="n">
-        <v>1.859339360402736</v>
-      </c>
-    </row>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="F43" s="7" t="n">
+        <v>19.62168778003666</v>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="40" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>0.0003887133639875507</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>1.776152929443725</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0.0003887133639875507</v>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>VSUP, IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="40" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>VSUP, ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="40" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>a3cd1afe-76aa-432c-b637-52f2cb23dbb1</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>0.1729643427354296</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>1.681119494098833</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>1.748818207431798</v>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="40" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
         <is>
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Anzahl</t>
-        </is>
-      </c>
-      <c r="C10" s="7" t="n">
+      <c r="D47" s="7" t="n">
+        <v>61.00786621463389</v>
+      </c>
+      <c r="E47" s="7" t="n">
+        <v>38.97507927991641</v>
+      </c>
+      <c r="F47" s="7" t="n">
+        <v>39.56135878519856</v>
+      </c>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="40" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>1.219178171102477</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>0.8083777659039347</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>1.48976927354169</v>
+      </c>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="40" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>97.29244278871759</v>
+      </c>
+      <c r="F49" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>VSUP, IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="40" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>be55e91e-6926-4ccb-a615-4366dd10f191</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>3.562791534921518</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>2.520700936042364</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>2.084963841843242</v>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="40" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>50.81302353189629</v>
+      </c>
+      <c r="E51" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-      <c r="P10" s="4" t="n"/>
-      <c r="Q10" s="4" t="n"/>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="F51" s="7" t="n">
+        <v>6.49631944082691</v>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="40" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>IsoGlyph</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Prozent (%)</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="n">
+      <c r="D52" s="7" t="n">
+        <v>0.5810241674967406</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>0.007564393998705471</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>0.020408221347917</v>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="40" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>0.3631468553360225</v>
+      </c>
+      <c r="E53" s="7" t="n">
+        <v>0.2361628525810126</v>
+      </c>
+      <c r="F53" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="40" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>cf01aea4-edcc-4a98-a81b-253e2f3bfac3</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>1.67857590082322</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>0.04128447547194585</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0.04128447547194585</v>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph, IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="40" customHeight="1">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>4.612880656014729</v>
+      </c>
+      <c r="E55" s="7" t="n">
+        <v>30.88375849416899</v>
+      </c>
+      <c r="F55" s="7" t="n">
+        <v>2.849560205286445</v>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="40" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>0.1214329563811354</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>0.005902856443478786</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0.5810241674967406</v>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="40" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="E57" s="7" t="n">
+        <v>15.98080956704122</v>
+      </c>
+      <c r="F57" s="7" t="n">
+        <v>38.45365181729949</v>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="40" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>d299244f-cda7-4a50-8153-71c7d48e9787</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>99.8239050809254</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>43.15401652944321</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>57.02051310146209</v>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="40" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="D11" s="7" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="E11" s="7" t="n">
-        <v>6.67</v>
-      </c>
-      <c r="F11" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="G11" s="7" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>20</v>
-      </c>
-      <c r="I11" s="7" t="n">
-        <v>26.67</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>15</v>
-      </c>
-      <c r="K11" s="7" t="n">
+      <c r="E59" s="7" t="n">
+        <v>4.612880656014729</v>
+      </c>
+      <c r="F59" s="7" t="n">
+        <v>2.849560205286445</v>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="40" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>94.88420327656038</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>0.7467223193254292</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0.02262812341941233</v>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="40" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="n">
+        <v>2.268689540744398</v>
+      </c>
+      <c r="E61" s="7" t="n">
+        <v>0.2234448862035164</v>
+      </c>
+      <c r="F61" s="7" t="n">
+        <v>0.176094919074602</v>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="40" customHeight="1">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>e243988d-c3f7-4ea9-a86d-55f84c20923a</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>99.29170710327777</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>1.750383495601384</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>55.59570954512723</v>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="40" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="n">
+        <v>41.55797675598935</v>
+      </c>
+      <c r="E63" s="7" t="n">
+        <v>30.88375849416899</v>
+      </c>
+      <c r="F63" s="7" t="n">
+        <v>28.03910307379777</v>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="40" customHeight="1">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1.365807687183427</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>1.372383900488059</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>1.828030568151923</v>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="40" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>2.07146323138081</v>
+      </c>
+      <c r="E65" s="7" t="n">
+        <v>52.85704223147476</v>
+      </c>
+      <c r="F65" s="7" t="n">
+        <v>25.75603418589369</v>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="40" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>3.601728078139227</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>1.850561938452907</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>62.39825626897907</v>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="40" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="L11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="O11" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P11" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q11" s="7" t="n">
-        <v>1.772810520855837</v>
+      <c r="E67" s="7" t="n">
+        <v>27.91143955247274</v>
+      </c>
+      <c r="F67" s="7" t="n">
+        <v>2.849560205286445</v>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="40" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>0.0411195578526509</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>1.11089936248175</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>0.03443034855114319</v>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="40" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>0.7082928967222309</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>0.2361628525810126</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>0.2361628525810126</v>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph, IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="40" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>f6b6ef18-1646-4b1f-bc55-850497b42807</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>0.2553376326582298</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>0.2553376326582298</v>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph, IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="40" customHeight="1">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Maxima</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="7" t="n">
+        <v>2.849560205286445</v>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>VSUP, ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="40" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Niederschlag_Uncertainty_Minima</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>0.42070724375937</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>2.887021701273676</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>0.007414919955298784</v>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="40" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Maxima</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>0.7082928967222309</v>
+      </c>
+      <c r="E73" s="7" t="n">
+        <v>0.2361628525810126</v>
+      </c>
+      <c r="F73" s="7" t="n">
+        <v>0.7082928967222309</v>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>ScaledGlyph</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>Nein</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="40" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>fbbbd38b-c942-4986-ba5d-ec496c3b8560</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Luftdruck_Value_Minima</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>0.04128447547194585</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>3.378087530914334</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>0.2553376326582298</v>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>Ja</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A3:Q3"/>
-    <mergeCell ref="A1:Q1"/>
-    <mergeCell ref="A4:Q4"/>
+  <mergeCells count="5">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2861,7 +4978,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Feedback: Anstrengung</t>
+          <t>Feedback: Ablesbarkeit</t>
         </is>
       </c>
     </row>
@@ -2872,14 +4989,14 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Stufe 1–7: Anzahl und prozentualer Anteil; Median, Quartile, IQR, Mittelwert und Standardabweichung basieren auf gültigen Antworten.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Methode</t>
@@ -2978,25 +5095,25 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="7" t="n">
         <v>3</v>
-      </c>
-      <c r="D6" s="7" t="n">
-        <v>1</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>2</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G6" s="7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I6" s="7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J6" s="4" t="n"/>
       <c r="K6" s="4" t="n"/>
@@ -3019,49 +5136,49 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>6.67</v>
+        <v>17.65</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>13.33</v>
+        <v>11.76</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>13.33</v>
+        <v>17.65</v>
       </c>
       <c r="G7" s="7" t="n">
-        <v>40</v>
+        <v>5.88</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>6.67</v>
+        <v>17.65</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>0</v>
+        <v>29.41</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K7" s="7" t="n">
         <v>0</v>
       </c>
       <c r="L7" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="O7" s="7" t="n">
         <v>4</v>
       </c>
-      <c r="M7" s="7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>5</v>
-      </c>
-      <c r="O7" s="7" t="n">
-        <v>2.5</v>
-      </c>
       <c r="P7" s="7" t="n">
-        <v>3.666666666666667</v>
+        <v>4.823529411764706</v>
       </c>
       <c r="Q7" s="7" t="n">
-        <v>1.718249385968449</v>
+        <v>1.94407092584244</v>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
@@ -3076,25 +5193,25 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G8" s="7" t="n">
         <v>2</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I8" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
@@ -3117,49 +5234,49 @@
         </is>
       </c>
       <c r="C9" s="7" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>33.33</v>
+        <v>5.88</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>26.67</v>
+        <v>17.65</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>13.33</v>
+        <v>5.88</v>
       </c>
       <c r="G9" s="7" t="n">
-        <v>13.33</v>
+        <v>11.76</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0</v>
+        <v>47.06</v>
       </c>
       <c r="I9" s="7" t="n">
-        <v>13.33</v>
+        <v>5.88</v>
       </c>
       <c r="J9" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="M9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="M9" s="7" t="n">
-        <v>2</v>
-      </c>
       <c r="N9" s="7" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="O9" s="7" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="P9" s="7" t="n">
-        <v>3.6</v>
+        <v>4.764705882352941</v>
       </c>
       <c r="Q9" s="7" t="n">
-        <v>1.723783214742669</v>
+        <v>1.751050105105001</v>
       </c>
     </row>
     <row r="10" ht="28" customHeight="1">
@@ -3174,25 +5291,25 @@
         </is>
       </c>
       <c r="C10" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I10" s="7" t="n">
         <v>4</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>4</v>
-      </c>
-      <c r="I10" s="7" t="n">
-        <v>0</v>
       </c>
       <c r="J10" s="4" t="n"/>
       <c r="K10" s="4" t="n"/>
@@ -3203,7 +5320,7 @@
       <c r="P10" s="4" t="n"/>
       <c r="Q10" s="4" t="n"/>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>IsoGlyph</t>
@@ -3215,28 +5332,28 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>13.33</v>
+        <v>11.76</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>13.33</v>
+        <v>5.88</v>
       </c>
       <c r="F11" s="7" t="n">
-        <v>13.33</v>
+        <v>23.53</v>
       </c>
       <c r="G11" s="7" t="n">
-        <v>26.67</v>
+        <v>17.65</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>26.67</v>
+        <v>17.65</v>
       </c>
       <c r="I11" s="7" t="n">
-        <v>0</v>
+        <v>23.53</v>
       </c>
       <c r="J11" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K11" s="7" t="n">
         <v>0</v>
@@ -3245,19 +5362,19 @@
         <v>5</v>
       </c>
       <c r="M11" s="7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N11" s="7" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="O11" s="7" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="P11" s="7" t="n">
-        <v>4.2</v>
+        <v>4.941176470588236</v>
       </c>
       <c r="Q11" s="7" t="n">
-        <v>1.65615734242165</v>
+        <v>1.675954512930397</v>
       </c>
     </row>
   </sheetData>
@@ -3276,6 +5393,446 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:Q11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="21" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Feedback: Anstrengung</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Antwortverteilung und Kennzahlen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Stufe 1–7: Anzahl und prozentualer Anteil; Median, Quartile, IQR, Mittelwert und Standardabweichung basieren auf gültigen Antworten.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Methode</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Angabe</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Stufe 1</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>Stufe 2</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Stufe 3</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Stufe 4</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Stufe 5</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Stufe 6</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Stufe 7</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>Fehlend</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>Median</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t>IQR</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>Mittelwert</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>Standardabweichung</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="28" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Anzahl</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="4" t="n"/>
+      <c r="L6" s="4" t="n"/>
+      <c r="M6" s="4" t="n"/>
+      <c r="N6" s="4" t="n"/>
+      <c r="O6" s="4" t="n"/>
+      <c r="P6" s="4" t="n"/>
+      <c r="Q6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="40" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>VSUP</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Prozent (%)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="F7" s="7" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="G7" s="7" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="K7" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P7" s="7" t="n">
+        <v>3.529411764705882</v>
+      </c>
+      <c r="Q7" s="7" t="n">
+        <v>1.662740473541479</v>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Scaled Glyph</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Anzahl</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Scaled Glyph</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Prozent (%)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="E9" s="7" t="n">
+        <v>29.41</v>
+      </c>
+      <c r="F9" s="7" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="G9" s="7" t="n">
+        <v>17.65</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="K9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="P9" s="7" t="n">
+        <v>3.647058823529412</v>
+      </c>
+      <c r="Q9" s="7" t="n">
+        <v>1.656093916063799</v>
+      </c>
+    </row>
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Anzahl</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+      <c r="M10" s="4" t="n"/>
+      <c r="N10" s="4" t="n"/>
+      <c r="O10" s="4" t="n"/>
+      <c r="P10" s="4" t="n"/>
+      <c r="Q10" s="4" t="n"/>
+    </row>
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>IsoGlyph</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Prozent (%)</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="F11" s="7" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="G11" s="7" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>23.53</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>17</v>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="P11" s="7" t="n">
+        <v>4.176470588235294</v>
+      </c>
+      <c r="Q11" s="7" t="n">
+        <v>1.550616575658174</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A3:Q3"/>
+    <mergeCell ref="A1:Q1"/>
+    <mergeCell ref="A4:Q4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3283,7 +5840,7 @@
     <col width="26" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="25" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -3301,14 +5858,14 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="40" customHeight="1">
+    <row r="4" ht="46" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Verbundenes Design: dieselben Personen bewerten alle drei Methoden. Friedman als Gesamttest; bei p &lt; 0,05 Wilcoxon-Paarvergleiche mit Holm-Korrektur.</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>Merkmal</t>
@@ -3340,7 +5897,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Rangfolge</t>
@@ -3352,7 +5909,7 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D6" s="4" t="n"/>
       <c r="E6" s="4" t="n"/>
@@ -3370,13 +5927,13 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>2.285714285714278</v>
+        <v>1.125</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>0.3189065573239717</v>
+        <v>0.569782824730923</v>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
@@ -3384,7 +5941,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Ablesbarkeit</t>
@@ -3396,13 +5953,13 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D8" s="4" t="n"/>
       <c r="E8" s="4" t="n"/>
       <c r="F8" s="4" t="n"/>
     </row>
-    <row r="9" ht="28" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>Ablesbarkeit</t>
@@ -3414,13 +5971,13 @@
         </is>
       </c>
       <c r="C9" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>0.4642857142857184</v>
+        <v>0.3809523809523719</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>0.7928328533799686</v>
+        <v>0.8265654376242417</v>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
@@ -3428,7 +5985,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>Anstrengung</t>
@@ -3440,13 +5997,13 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D10" s="4" t="n"/>
       <c r="E10" s="4" t="n"/>
       <c r="F10" s="4" t="n"/>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>Anstrengung</t>
@@ -3458,13 +6015,13 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>0.4727272727272769</v>
+        <v>1.365079365079351</v>
       </c>
       <c r="E11" s="7" t="n">
-        <v>0.7894935331710372</v>
+        <v>0.5053319784901208</v>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
@@ -3482,7 +6039,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3516,7 +6073,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="42" customHeight="1">
+    <row r="5" ht="36" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>participantId</t>
@@ -3528,7 +6085,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="28" customHeight="1">
+    <row r="6" ht="55" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>29f255aa-1285-4664-9c07-0f88b583bd3b</t>
@@ -3540,7 +6097,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="28" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>4514dbd4-54fe-40d2-96d6-27bbb7accc29</t>
@@ -3552,7 +6109,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>500e39fd-101a-4580-a6be-ae82ef7f18b1</t>
@@ -3564,7 +6121,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="28" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>86e7d467-4933-49c3-a11a-6e322d55f191</t>
@@ -3576,7 +6133,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="28" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>9edd5d78-5949-4094-818b-ed11035f0353</t>
@@ -3588,7 +6145,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>e4bec96d-b98b-4a55-baeb-44d6ab1532b3</t>
